--- a/diseases/d183/2020-2025.xlsx
+++ b/diseases/d183/2020-2025.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1653,9 +1650,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2393,9 +2387,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -3133,9 +3124,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4021,9 +4009,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -4761,9 +4746,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5501,9 +5483,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6389,9 +6368,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -7129,9 +7105,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7869,9 +7842,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8757,9 +8727,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -9497,9 +9464,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10385,9 +10349,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -11125,9 +11086,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -11865,9 +11823,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12605,9 +12560,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -13493,9 +13445,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -14233,9 +14182,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -14973,9 +14919,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -15861,9 +15804,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -16601,9 +16541,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17489,9 +17426,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -18229,9 +18163,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -18969,9 +18900,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -19857,9 +19785,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -20597,9 +20522,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -21337,9 +21259,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -22225,9 +22144,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -22965,9 +22881,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -23705,9 +23618,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -24593,9 +24503,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -25333,9 +25240,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -26073,9 +25977,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -26961,9 +26862,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -27701,9 +27599,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -28441,9 +28336,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -29329,9 +29221,6 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0</v>
       </c>
@@ -30069,9 +29958,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -30809,9 +30695,6 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
@@ -31697,9 +31580,6 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -32437,9 +32317,6 @@
       <c r="O216" t="n">
         <v>0</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0</v>
       </c>
@@ -33177,9 +33054,6 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
@@ -34065,9 +33939,6 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0</v>
       </c>
@@ -34805,9 +34676,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -35693,9 +35561,6 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
@@ -36433,9 +36298,6 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
@@ -37173,9 +37035,6 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -38061,9 +37920,6 @@
       <c r="O254" t="n">
         <v>0</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0</v>
       </c>
@@ -38801,9 +38657,6 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -39541,9 +39394,6 @@
       <c r="O264" t="n">
         <v>0</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0</v>
       </c>
@@ -40429,9 +40279,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
@@ -41169,9 +41016,6 @@
       <c r="O275" t="n">
         <v>0</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0</v>
       </c>
@@ -41909,9 +41753,6 @@
       <c r="O280" t="n">
         <v>0</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0</v>
       </c>
@@ -42797,9 +42638,6 @@
       <c r="O286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0</v>
       </c>
@@ -43537,9 +43375,6 @@
       <c r="O291" t="n">
         <v>0</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0</v>
       </c>
@@ -44277,9 +44112,6 @@
       <c r="O296" t="n">
         <v>0</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0</v>
       </c>
@@ -45165,9 +44997,6 @@
       <c r="O302" t="n">
         <v>0</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0</v>
       </c>
@@ -45905,9 +45734,6 @@
       <c r="O307" t="n">
         <v>0</v>
       </c>
-      <c r="Q307" t="n">
-        <v>0</v>
-      </c>
       <c r="R307" t="n">
         <v>0</v>
       </c>
@@ -46793,9 +46619,6 @@
       <c r="O313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0</v>
       </c>
@@ -47533,9 +47356,6 @@
       <c r="O318" t="n">
         <v>0</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0</v>
       </c>
@@ -48273,9 +48093,6 @@
       <c r="O323" t="n">
         <v>0</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0</v>
       </c>
@@ -49161,9 +48978,6 @@
       <c r="O329" t="n">
         <v>0</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0</v>
       </c>
@@ -49901,9 +49715,6 @@
       <c r="O334" t="n">
         <v>0</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0</v>
       </c>
@@ -50641,9 +50452,6 @@
       <c r="O339" t="n">
         <v>0</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0</v>
       </c>
@@ -51381,9 +51189,6 @@
       <c r="O344" t="n">
         <v>0</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>0</v>
       </c>
@@ -52269,9 +52074,6 @@
       <c r="O350" t="n">
         <v>0</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>0</v>
       </c>
@@ -53009,9 +52811,6 @@
       <c r="O355" t="n">
         <v>0</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0</v>
       </c>
@@ -53897,9 +53696,6 @@
       <c r="O361" t="n">
         <v>0</v>
       </c>
-      <c r="Q361" t="n">
-        <v>0</v>
-      </c>
       <c r="R361" t="n">
         <v>0</v>
       </c>
@@ -54637,9 +54433,6 @@
       <c r="O366" t="n">
         <v>0</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0</v>
       </c>
@@ -55377,9 +55170,6 @@
       <c r="O371" t="n">
         <v>0</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0</v>
       </c>
@@ -56265,9 +56055,6 @@
       <c r="O377" t="n">
         <v>0</v>
       </c>
-      <c r="Q377" t="n">
-        <v>0</v>
-      </c>
       <c r="R377" t="n">
         <v>0</v>
       </c>
@@ -57003,9 +56790,6 @@
         <v>0</v>
       </c>
       <c r="O382" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q382" t="n">
         <v>0</v>
       </c>
       <c r="R382" t="n">
